--- a/PAINEL_MEDICAO.xlsx
+++ b/PAINEL_MEDICAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fe382923eb6bfb95/Área de Trabalho/EMPRESA/LEONE/ADMINISTRATIVO/ALEX/DASH_MENSAL/dashboard-financeiro-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="8_{80296205-AFED-4F77-986A-C43D9A802F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83B138A6-A9E0-4E3F-AA60-2A16AB5ACBED}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="8_{80296205-AFED-4F77-986A-C43D9A802F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC174C9E-6F20-446F-82B2-5F27795BC1B0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D458C61B-3165-4ACA-B3D1-BE54D26DDE28}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$F$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$F$87</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="29">
   <si>
     <t>SAFRA</t>
   </si>
@@ -123,6 +123,9 @@
   </si>
   <si>
     <t>CAMARA MUNICIPAL - NAZARENO</t>
+  </si>
+  <si>
+    <t>QUADRA CONFUSÃO</t>
   </si>
 </sst>
 </file>
@@ -590,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78C61581-3CDE-422B-802B-087CF49FF933}">
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -815,7 +818,7 @@
         <v>46105</v>
       </c>
       <c r="B11" s="1" t="str">
-        <f t="shared" ref="B11:B26" si="0">TEXT(A11,"AAAA-MM")</f>
+        <f>TEXT(A11,"AAAA-MM")</f>
         <v>2026-03</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -836,7 +839,7 @@
         <v>46150</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A12,"AAAA-MM")</f>
         <v>2026-05</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -857,7 +860,7 @@
         <v>46149</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A13,"AAAA-MM")</f>
         <v>2026-05</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -878,7 +881,7 @@
         <v>46135</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A14,"AAAA-MM")</f>
         <v>2026-04</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -899,7 +902,7 @@
         <v>46153</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A15,"AAAA-MM")</f>
         <v>2026-05</v>
       </c>
       <c r="C15" s="4" t="s">
@@ -920,7 +923,7 @@
         <v>46153</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A16,"AAAA-MM")</f>
         <v>2026-05</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -941,7 +944,7 @@
         <v>46148</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A17,"AAAA-MM")</f>
         <v>2026-05</v>
       </c>
       <c r="C17" s="4" t="s">
@@ -962,7 +965,7 @@
         <v>46148</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A18,"AAAA-MM")</f>
         <v>2026-05</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -983,7 +986,7 @@
         <v>46161</v>
       </c>
       <c r="B19" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A19,"AAAA-MM")</f>
         <v>2026-05</v>
       </c>
       <c r="C19" s="4" t="s">
@@ -1004,7 +1007,7 @@
         <v>46147</v>
       </c>
       <c r="B20" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A20,"AAAA-MM")</f>
         <v>2026-05</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -1025,7 +1028,7 @@
         <v>46150</v>
       </c>
       <c r="B21" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A21,"AAAA-MM")</f>
         <v>2026-05</v>
       </c>
       <c r="C21" s="4" t="s">
@@ -1046,7 +1049,7 @@
         <v>46157</v>
       </c>
       <c r="B22" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A22,"AAAA-MM")</f>
         <v>2026-05</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -1067,7 +1070,7 @@
         <v>46161</v>
       </c>
       <c r="B23" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A23,"AAAA-MM")</f>
         <v>2026-05</v>
       </c>
       <c r="C23" s="4" t="s">
@@ -1088,7 +1091,7 @@
         <v>46196</v>
       </c>
       <c r="B24" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A24,"AAAA-MM")</f>
         <v>2026-06</v>
       </c>
       <c r="C24" s="4" t="s">
@@ -1109,11 +1112,11 @@
         <v>46184</v>
       </c>
       <c r="B25" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A25,"AAAA-MM")</f>
         <v>2026-06</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>8</v>
@@ -1130,7 +1133,7 @@
         <v>46184</v>
       </c>
       <c r="B26" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>TEXT(A26,"AAAA-MM")</f>
         <v>2026-06</v>
       </c>
       <c r="C26" s="4" t="s">
@@ -1179,8 +1182,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="3"/>
-      <c r="B29" s="1"/>
+      <c r="A29" s="3">
+        <v>46206</v>
+      </c>
+      <c r="B29" s="1" t="str">
+        <f>TEXT(A29,"AAAA-MM")</f>
+        <v>2026-07</v>
+      </c>
       <c r="C29" s="4" t="s">
         <v>5</v>
       </c>
@@ -1195,8 +1203,13 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="3"/>
-      <c r="B30" s="1"/>
+      <c r="A30" s="3">
+        <v>46206</v>
+      </c>
+      <c r="B30" s="1" t="str">
+        <f>TEXT(A30,"AAAA-MM")</f>
+        <v>2026-07</v>
+      </c>
       <c r="C30" s="4" t="s">
         <v>5</v>
       </c>
@@ -1211,204 +1224,159 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
-        <v>46031</v>
-      </c>
-      <c r="B31" s="1" t="str">
-        <f>TEXT(A31,"AAAA-MM")</f>
-        <v>2026-01</v>
-      </c>
+      <c r="A31" s="3"/>
+      <c r="B31" s="1"/>
       <c r="C31" s="4" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F31" s="5">
-        <v>175344.01</v>
+        <v>5938.07</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
-        <v>46050</v>
-      </c>
-      <c r="B32" s="1" t="str">
-        <f>TEXT(A32,"AAAA-MM")</f>
-        <v>2026-01</v>
-      </c>
+      <c r="A32" s="3"/>
+      <c r="B32" s="1"/>
       <c r="C32" s="4" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F32" s="5">
-        <v>49479.11</v>
+        <v>4317.3599999999997</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
-        <v>46055</v>
-      </c>
-      <c r="B33" s="1" t="str">
-        <f>TEXT(A33,"AAAA-MM")</f>
-        <v>2026-02</v>
-      </c>
+      <c r="A33" s="3"/>
+      <c r="B33" s="1"/>
       <c r="C33" s="4" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F33" s="5">
-        <v>82294.75</v>
+        <v>109050.83</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
-        <v>46073</v>
-      </c>
-      <c r="B34" s="1" t="str">
-        <f>TEXT(A34,"AAAA-MM")</f>
-        <v>2026-02</v>
-      </c>
+      <c r="A34" s="3"/>
+      <c r="B34" s="1"/>
       <c r="C34" s="4" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F34" s="5">
-        <v>99660.65</v>
+        <v>7493.59</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
-        <v>46066</v>
-      </c>
-      <c r="B35" s="1" t="str">
-        <f>TEXT(A35,"AAAA-MM")</f>
-        <v>2026-02</v>
-      </c>
+      <c r="A35" s="3"/>
+      <c r="B35" s="1"/>
       <c r="C35" s="4" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F35" s="5">
-        <v>33014.82</v>
+        <v>18558.21</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
-        <v>46086</v>
-      </c>
-      <c r="B36" s="1" t="str">
-        <f>TEXT(A36,"AAAA-MM")</f>
-        <v>2026-03</v>
-      </c>
+      <c r="A36" s="3"/>
+      <c r="B36" s="1"/>
       <c r="C36" s="4" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F36" s="5">
-        <v>113652.43</v>
+        <v>166317.79999999999</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
-        <v>46099</v>
-      </c>
-      <c r="B37" s="1" t="str">
-        <f>TEXT(A37,"AAAA-MM")</f>
-        <v>2026-03</v>
-      </c>
+      <c r="A37" s="3"/>
+      <c r="B37" s="1"/>
       <c r="C37" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F37" s="5">
-        <v>240884.01</v>
+        <v>130602.76</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
-        <v>46100</v>
-      </c>
-      <c r="B38" s="1" t="str">
-        <f>TEXT(A38,"AAAA-MM")</f>
-        <v>2026-03</v>
-      </c>
+      <c r="A38" s="3"/>
+      <c r="B38" s="1"/>
       <c r="C38" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F38" s="5">
-        <v>118242.07</v>
+        <v>4915.72</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
-        <v>46113</v>
-      </c>
-      <c r="B39" s="1" t="str">
-        <f>TEXT(A39,"AAAA-MM")</f>
-        <v>2026-04</v>
-      </c>
+      <c r="A39" s="3"/>
+      <c r="B39" s="1"/>
       <c r="C39" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F39" s="5">
-        <v>9677.83</v>
+        <v>14780.71</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
-        <v>46114</v>
+        <v>46031</v>
       </c>
       <c r="B40" s="1" t="str">
-        <f t="shared" ref="B40:B58" si="1">TEXT(A40,"AAAA-MM")</f>
-        <v>2026-04</v>
+        <f>TEXT(A40,"AAAA-MM")</f>
+        <v>2026-01</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>15</v>
@@ -1417,19 +1385,19 @@
         <v>19</v>
       </c>
       <c r="F40" s="5">
-        <v>49479.11</v>
+        <v>175344.01</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
-        <v>46119</v>
+        <v>46050</v>
       </c>
       <c r="B41" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>2026-04</v>
+        <f>TEXT(A41,"AAAA-MM")</f>
+        <v>2026-01</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>15</v>
@@ -1438,19 +1406,19 @@
         <v>19</v>
       </c>
       <c r="F41" s="5">
-        <v>66130.100000000006</v>
+        <v>49479.11</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
-        <v>46125</v>
+        <v>46055</v>
       </c>
       <c r="B42" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>2026-04</v>
+        <f>TEXT(A42,"AAAA-MM")</f>
+        <v>2026-02</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>15</v>
@@ -1459,19 +1427,19 @@
         <v>19</v>
       </c>
       <c r="F42" s="5">
-        <v>16640.05</v>
+        <v>82294.75</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
-        <v>46125</v>
+        <v>46073</v>
       </c>
       <c r="B43" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>2026-04</v>
+        <f>TEXT(A43,"AAAA-MM")</f>
+        <v>2026-02</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>15</v>
@@ -1480,19 +1448,19 @@
         <v>19</v>
       </c>
       <c r="F43" s="5">
-        <v>17563.47</v>
+        <v>99660.65</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
-        <v>46142</v>
+        <v>46066</v>
       </c>
       <c r="B44" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>2026-04</v>
+        <f>TEXT(A44,"AAAA-MM")</f>
+        <v>2026-02</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>15</v>
@@ -1501,19 +1469,19 @@
         <v>19</v>
       </c>
       <c r="F44" s="5">
-        <v>53404.84</v>
+        <v>33014.82</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
-        <v>46140</v>
+        <v>46086</v>
       </c>
       <c r="B45" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>2026-04</v>
+        <f>TEXT(A45,"AAAA-MM")</f>
+        <v>2026-03</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>15</v>
@@ -1522,19 +1490,19 @@
         <v>19</v>
       </c>
       <c r="F45" s="5">
-        <v>33014.82</v>
+        <v>113652.43</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
-        <v>46154</v>
+        <v>46099</v>
       </c>
       <c r="B46" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>2026-05</v>
+        <f>TEXT(A46,"AAAA-MM")</f>
+        <v>2026-03</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>15</v>
@@ -1543,19 +1511,19 @@
         <v>19</v>
       </c>
       <c r="F46" s="5">
-        <v>159944.82999999999</v>
+        <v>240884.01</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
-        <v>46169</v>
+        <v>46100</v>
       </c>
       <c r="B47" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>2026-05</v>
+        <f>TEXT(A47,"AAAA-MM")</f>
+        <v>2026-03</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>15</v>
@@ -1564,19 +1532,19 @@
         <v>19</v>
       </c>
       <c r="F47" s="5">
-        <v>172055.23</v>
+        <v>118242.07</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
-        <v>46169</v>
+        <v>46113</v>
       </c>
       <c r="B48" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>2026-05</v>
+        <f>TEXT(A48,"AAAA-MM")</f>
+        <v>2026-04</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>15</v>
@@ -1585,19 +1553,19 @@
         <v>19</v>
       </c>
       <c r="F48" s="5">
-        <v>28101.02</v>
+        <v>9677.83</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
-        <v>46154</v>
+        <v>46114</v>
       </c>
       <c r="B49" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>2026-05</v>
+        <f>TEXT(A49,"AAAA-MM")</f>
+        <v>2026-04</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>15</v>
@@ -1606,16 +1574,16 @@
         <v>19</v>
       </c>
       <c r="F49" s="5">
-        <v>71475.05</v>
+        <v>49479.11</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
-        <v>46154</v>
+        <v>46119</v>
       </c>
       <c r="B50" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>2026-05</v>
+        <f>TEXT(A50,"AAAA-MM")</f>
+        <v>2026-04</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>22</v>
@@ -1627,19 +1595,19 @@
         <v>19</v>
       </c>
       <c r="F50" s="5">
-        <v>62994.13</v>
+        <v>66130.100000000006</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
-        <v>46181</v>
+        <v>46125</v>
       </c>
       <c r="B51" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>2026-06</v>
+        <f>TEXT(A51,"AAAA-MM")</f>
+        <v>2026-04</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>15</v>
@@ -1648,19 +1616,19 @@
         <v>19</v>
       </c>
       <c r="F51" s="5">
-        <v>12964.48</v>
+        <v>16640.05</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
-        <v>46181</v>
+        <v>46125</v>
       </c>
       <c r="B52" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>2026-06</v>
+        <f>TEXT(A52,"AAAA-MM")</f>
+        <v>2026-04</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>15</v>
@@ -1669,16 +1637,16 @@
         <v>19</v>
       </c>
       <c r="F52" s="5">
-        <v>43881.86</v>
+        <v>17563.47</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
-        <v>46183</v>
+        <v>46142</v>
       </c>
       <c r="B53" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>2026-06</v>
+        <f>TEXT(A53,"AAAA-MM")</f>
+        <v>2026-04</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>14</v>
@@ -1690,19 +1658,19 @@
         <v>19</v>
       </c>
       <c r="F53" s="5">
-        <v>116713.56</v>
+        <v>53404.84</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
-        <v>46183</v>
+        <v>46140</v>
       </c>
       <c r="B54" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>2026-06</v>
+        <f>TEXT(A54,"AAAA-MM")</f>
+        <v>2026-04</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>15</v>
@@ -1711,19 +1679,19 @@
         <v>19</v>
       </c>
       <c r="F54" s="5">
-        <v>12545.33</v>
+        <v>33014.82</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
-        <v>46184</v>
+        <v>46154</v>
       </c>
       <c r="B55" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>2026-06</v>
+        <f>TEXT(A55,"AAAA-MM")</f>
+        <v>2026-05</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>15</v>
@@ -1732,14 +1700,19 @@
         <v>19</v>
       </c>
       <c r="F55" s="5">
-        <v>49479.11</v>
+        <v>159944.82999999999</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="3"/>
-      <c r="B56" s="1"/>
+      <c r="A56" s="3">
+        <v>46169</v>
+      </c>
+      <c r="B56" s="1" t="str">
+        <f>TEXT(A56,"AAAA-MM")</f>
+        <v>2026-05</v>
+      </c>
       <c r="C56" s="4" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>15</v>
@@ -1748,14 +1721,19 @@
         <v>19</v>
       </c>
       <c r="F56" s="5">
-        <v>23760.73</v>
+        <v>172055.23</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="3"/>
-      <c r="B57" s="1"/>
+      <c r="A57" s="3">
+        <v>46169</v>
+      </c>
+      <c r="B57" s="1" t="str">
+        <f>TEXT(A57,"AAAA-MM")</f>
+        <v>2026-05</v>
+      </c>
       <c r="C57" s="4" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>15</v>
@@ -1764,51 +1742,61 @@
         <v>19</v>
       </c>
       <c r="F57" s="5">
-        <v>14926.37</v>
+        <v>28101.02</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
-        <v>46202</v>
+        <v>46154</v>
       </c>
       <c r="B58" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>TEXT(A58,"AAAA-MM")</f>
+        <v>2026-05</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F58" s="5">
+        <v>71475.05</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="3">
+        <v>46154</v>
+      </c>
+      <c r="B59" s="1" t="str">
+        <f>TEXT(A59,"AAAA-MM")</f>
+        <v>2026-05</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F59" s="5">
+        <v>62994.13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
+        <v>46181</v>
+      </c>
+      <c r="B60" s="1" t="str">
+        <f>TEXT(A60,"AAAA-MM")</f>
         <v>2026-06</v>
       </c>
-      <c r="C58" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F58" s="5">
-        <v>79682.429999999993</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="3"/>
-      <c r="B59" s="1"/>
-      <c r="C59" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F59" s="5">
-        <v>11922.88</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="3"/>
-      <c r="B60" s="1"/>
       <c r="C60" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>15</v>
@@ -1817,14 +1805,19 @@
         <v>19</v>
       </c>
       <c r="F60" s="5">
-        <v>10036.26</v>
+        <v>12964.48</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="3"/>
-      <c r="B61" s="1"/>
+      <c r="A61" s="3">
+        <v>46181</v>
+      </c>
+      <c r="B61" s="1" t="str">
+        <f>TEXT(A61,"AAAA-MM")</f>
+        <v>2026-06</v>
+      </c>
       <c r="C61" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>15</v>
@@ -1833,229 +1826,209 @@
         <v>19</v>
       </c>
       <c r="F61" s="5">
-        <v>89122.7</v>
+        <v>43881.86</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
-        <v>46072</v>
+        <v>46183</v>
       </c>
       <c r="B62" s="1" t="str">
         <f>TEXT(A62,"AAAA-MM")</f>
-        <v>2026-02</v>
+        <v>2026-06</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F62" s="5">
-        <v>283719.89</v>
+        <v>116713.56</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
-        <v>46052</v>
+        <v>46183</v>
       </c>
       <c r="B63" s="1" t="str">
         <f>TEXT(A63,"AAAA-MM")</f>
-        <v>2026-01</v>
+        <v>2026-06</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F63" s="5">
-        <v>37071.980000000003</v>
+        <v>12545.33</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
-        <v>46050</v>
+        <v>46184</v>
       </c>
       <c r="B64" s="1" t="str">
         <f>TEXT(A64,"AAAA-MM")</f>
-        <v>2026-01</v>
+        <v>2026-06</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F64" s="5">
-        <v>52435.14</v>
+        <v>49479.11</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
-        <v>46080</v>
+        <v>46203</v>
       </c>
       <c r="B65" s="1" t="str">
         <f>TEXT(A65,"AAAA-MM")</f>
-        <v>2026-02</v>
+        <v>2026-06</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F65" s="5">
-        <v>21893.759999999998</v>
+        <v>23760.73</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
-        <v>46080</v>
+        <v>46203</v>
       </c>
       <c r="B66" s="1" t="str">
         <f>TEXT(A66,"AAAA-MM")</f>
-        <v>2026-02</v>
+        <v>2026-06</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F66" s="5">
-        <v>33292.76</v>
+        <v>14926.37</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
-        <v>46078</v>
+        <v>46202</v>
       </c>
       <c r="B67" s="1" t="str">
         <f>TEXT(A67,"AAAA-MM")</f>
-        <v>2026-02</v>
+        <v>2026-06</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F67" s="5">
-        <v>1738.58</v>
+        <v>79682.429999999993</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="3">
-        <v>46080</v>
-      </c>
-      <c r="B68" s="1" t="str">
-        <f>TEXT(A68,"AAAA-MM")</f>
-        <v>2026-02</v>
-      </c>
+      <c r="A68" s="3"/>
+      <c r="B68" s="1"/>
       <c r="C68" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F68" s="5">
-        <v>4750.45</v>
+        <v>11922.88</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="3">
-        <v>46121</v>
-      </c>
-      <c r="B69" s="1" t="str">
-        <f>TEXT(A69,"AAAA-MM")</f>
-        <v>2026-04</v>
-      </c>
+      <c r="A69" s="3"/>
+      <c r="B69" s="1"/>
       <c r="C69" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F69" s="5">
-        <v>62541.57</v>
+        <v>10036.26</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="3">
-        <v>46146</v>
-      </c>
-      <c r="B70" s="1" t="str">
-        <f t="shared" ref="B70:B77" si="2">TEXT(A70,"AAAA-MM")</f>
-        <v>2026-05</v>
-      </c>
+      <c r="A70" s="3"/>
+      <c r="B70" s="1"/>
       <c r="C70" s="4" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F70" s="5">
-        <v>55985.64</v>
+        <v>89122.7</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="3">
-        <v>46169</v>
-      </c>
-      <c r="B71" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>2026-05</v>
-      </c>
+      <c r="A71" s="3"/>
+      <c r="B71" s="1"/>
       <c r="C71" s="4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F71" s="5">
-        <v>154142.54</v>
+        <v>139858.12</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
-        <v>46169</v>
+        <v>46072</v>
       </c>
       <c r="B72" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>2026-05</v>
+        <f>TEXT(A72,"AAAA-MM")</f>
+        <v>2026-02</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>11</v>
@@ -2064,19 +2037,19 @@
         <v>19</v>
       </c>
       <c r="F72" s="5">
-        <v>51257.36</v>
+        <v>283719.89</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
-        <v>46157</v>
+        <v>46052</v>
       </c>
       <c r="B73" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>2026-05</v>
+        <f>TEXT(A73,"AAAA-MM")</f>
+        <v>2026-01</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>11</v>
@@ -2085,19 +2058,19 @@
         <v>19</v>
       </c>
       <c r="F73" s="5">
-        <v>320442.87</v>
+        <v>37071.980000000003</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
-        <v>46168</v>
+        <v>46050</v>
       </c>
       <c r="B74" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>2026-05</v>
+        <f>TEXT(A74,"AAAA-MM")</f>
+        <v>2026-01</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>11</v>
@@ -2106,19 +2079,19 @@
         <v>19</v>
       </c>
       <c r="F74" s="5">
-        <v>20501.97</v>
+        <v>52435.14</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
-        <v>46169</v>
+        <v>46080</v>
       </c>
       <c r="B75" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>2026-05</v>
+        <f>TEXT(A75,"AAAA-MM")</f>
+        <v>2026-02</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>11</v>
@@ -2127,19 +2100,19 @@
         <v>19</v>
       </c>
       <c r="F75" s="5">
-        <v>57227.58</v>
+        <v>21893.759999999998</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
-        <v>46184</v>
+        <v>46080</v>
       </c>
       <c r="B76" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>2026-06</v>
+        <f>TEXT(A76,"AAAA-MM")</f>
+        <v>2026-02</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>11</v>
@@ -2148,19 +2121,19 @@
         <v>19</v>
       </c>
       <c r="F76" s="5">
-        <v>45259.99</v>
+        <v>33292.76</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
-        <v>46198</v>
+        <v>46078</v>
       </c>
       <c r="B77" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>2026-06</v>
+        <f>TEXT(A77,"AAAA-MM")</f>
+        <v>2026-02</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>11</v>
@@ -2169,15 +2142,221 @@
         <v>19</v>
       </c>
       <c r="F77" s="5">
+        <v>1738.58</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B78" s="1" t="str">
+        <f>TEXT(A78,"AAAA-MM")</f>
+        <v>2026-02</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F78" s="5">
+        <v>4750.45</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="3">
+        <v>46121</v>
+      </c>
+      <c r="B79" s="1" t="str">
+        <f>TEXT(A79,"AAAA-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F79" s="5">
+        <v>62541.57</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="3">
+        <v>46146</v>
+      </c>
+      <c r="B80" s="1" t="str">
+        <f>TEXT(A80,"AAAA-MM")</f>
+        <v>2026-05</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F80" s="5">
+        <v>55985.64</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="3">
+        <v>46169</v>
+      </c>
+      <c r="B81" s="1" t="str">
+        <f>TEXT(A81,"AAAA-MM")</f>
+        <v>2026-05</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F81" s="5">
+        <v>154142.54</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="3">
+        <v>46169</v>
+      </c>
+      <c r="B82" s="1" t="str">
+        <f>TEXT(A82,"AAAA-MM")</f>
+        <v>2026-05</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F82" s="5">
+        <v>51257.36</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="3">
+        <v>46157</v>
+      </c>
+      <c r="B83" s="1" t="str">
+        <f>TEXT(A83,"AAAA-MM")</f>
+        <v>2026-05</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83" s="5">
+        <v>320442.87</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="3">
+        <v>46168</v>
+      </c>
+      <c r="B84" s="1" t="str">
+        <f>TEXT(A84,"AAAA-MM")</f>
+        <v>2026-05</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F84" s="5">
+        <v>20501.97</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="3">
+        <v>46169</v>
+      </c>
+      <c r="B85" s="1" t="str">
+        <f>TEXT(A85,"AAAA-MM")</f>
+        <v>2026-05</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F85" s="5">
+        <v>57227.58</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="3">
+        <v>46184</v>
+      </c>
+      <c r="B86" s="1" t="str">
+        <f>TEXT(A86,"AAAA-MM")</f>
+        <v>2026-06</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F86" s="5">
+        <v>45259.99</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="3">
+        <v>46198</v>
+      </c>
+      <c r="B87" s="1" t="str">
+        <f>TEXT(A87,"AAAA-MM")</f>
+        <v>2026-06</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F87" s="5">
         <v>44307.7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F69" xr:uid="{78C61581-3CDE-422B-802B-087CF49FF933}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F69">
-      <sortCondition ref="D1:D69"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:F87" xr:uid="{78C61581-3CDE-422B-802B-087CF49FF933}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>